--- a/Banlic-Mamatid_traci/batch_results/DQN_Results.xlsx
+++ b/Banlic-Mamatid_traci/batch_results/DQN_Results.xlsx
@@ -627,16 +627,16 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>68.1099</v>
+        <v>91.0441</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>118.9862</v>
+        <v>134.3594</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>9.7232</v>
+        <v>14.8272</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>2695.1625</v>
+        <v>3120.8496</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>68.7739</v>
+        <v>90.6842</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>111.2709</v>
+        <v>144.0746</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>10.4602</v>
+        <v>15.8633</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2651.5554</v>
+        <v>2977.6744</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -665,16 +665,16 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>71.1678</v>
+        <v>95.96720000000001</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>109.9898</v>
+        <v>133.2317</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10.1764</v>
+        <v>15.3177</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>2715.9027</v>
+        <v>3020.658</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
@@ -684,16 +684,16 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>69.289</v>
+        <v>90.023</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>116.2532</v>
+        <v>130.9509</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>9.7104</v>
+        <v>15.3685</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>2654.1061</v>
+        <v>3009.8899</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>68.3159</v>
+        <v>88.0667</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>112.6256</v>
+        <v>148.7422</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>9.8072</v>
+        <v>13.7849</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>2552.3008</v>
+        <v>2877.1679</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>70.1515</v>
+        <v>91.78019999999999</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>110.9349</v>
+        <v>142.1539</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>11.4766</v>
+        <v>16.1647</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2832.2753</v>
+        <v>2990.1346</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
@@ -741,16 +741,16 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>69.66679999999999</v>
+        <v>91.29259999999999</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>118.0509</v>
+        <v>142.8287</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>10.4897</v>
+        <v>14.9261</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2719.221</v>
+        <v>3087.3907</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
@@ -760,16 +760,16 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>72.1746</v>
+        <v>92.97839999999999</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>116.0841</v>
+        <v>129.2289</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>10.8876</v>
+        <v>15.9464</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>2740.9994</v>
+        <v>3176.0384</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
@@ -779,16 +779,16 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>70.035</v>
+        <v>96.574</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>106.5876</v>
+        <v>144.6458</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>10.7296</v>
+        <v>15.3794</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2754.6028</v>
+        <v>2946.0856</v>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>70.6138</v>
+        <v>90.3847</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>114.7528</v>
+        <v>132.9657</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>10.0722</v>
+        <v>16.2278</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2692.3983</v>
+        <v>3116.0644</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -824,16 +824,16 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>179.8554</v>
+        <v>448.6733</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>136.1956</v>
+        <v>179.1676</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>36.9333</v>
+        <v>47.5363</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>6045.561</v>
+        <v>4906.4854</v>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
@@ -843,16 +843,16 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>109.8539</v>
+        <v>142.9705</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>129.0713</v>
+        <v>145.2799</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>30.1823</v>
+        <v>37.6649</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>5616.523</v>
+        <v>6247.3951</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
@@ -862,16 +862,16 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>128.5555</v>
+        <v>137.6753</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>136.6993</v>
+        <v>143.2411</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>34.6261</v>
+        <v>37.3217</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>5711.0558</v>
+        <v>6121.7339</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
@@ -881,16 +881,16 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>101.5887</v>
+        <v>142.8683</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>125.3454</v>
+        <v>146.194</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>28.4056</v>
+        <v>37.1427</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>5554.4752</v>
+        <v>5990.433</v>
       </c>
     </row>
     <row r="20" ht="14" customHeight="1">
@@ -900,16 +900,16 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>110.8159</v>
+        <v>169.3983</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>121.8455</v>
+        <v>146.7084</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>30.4406</v>
+        <v>37.4768</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>5601.9161</v>
+        <v>5813.1459</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
@@ -919,16 +919,16 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>133.9924</v>
+        <v>163.2107</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>129.4708</v>
+        <v>138.8744</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>32.3656</v>
+        <v>35.0467</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>5578.0776</v>
+        <v>6178.0218</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
@@ -938,16 +938,16 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>92.5796</v>
+        <v>135.4547</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>115.6039</v>
+        <v>147.2321</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>29.3909</v>
+        <v>37.9502</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>5619.9552</v>
+        <v>6167.7065</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
@@ -957,16 +957,16 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>91.8663</v>
+        <v>154.3478</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>123.5552</v>
+        <v>145.4235</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>29.4465</v>
+        <v>39.7761</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>5814.3729</v>
+        <v>5851.4126</v>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>99.22410000000001</v>
+        <v>122.2749</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>128.5628</v>
+        <v>145.4628</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>30.3378</v>
+        <v>36.8626</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>5577.5426</v>
+        <v>5944.4737</v>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
@@ -995,16 +995,16 @@
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>157.4948</v>
+        <v>159.9393</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>137.9377</v>
+        <v>151.9719</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>35.4115</v>
+        <v>41.4015</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>5842.4741</v>
+        <v>6449.0203</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -1021,16 +1021,16 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>578.0872000000001</v>
+        <v>1013.5868</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>140.2409</v>
+        <v>184.5698</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>46.591</v>
+        <v>51.58</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>6385.4791</v>
+        <v>5227.2313</v>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
@@ -1040,16 +1040,16 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>548.9811999999999</v>
+        <v>849.7025</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>146.5978</v>
+        <v>148.4966</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>45.9192</v>
+        <v>50.441</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>6622.0186</v>
+        <v>5802.0523</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>582.9439</v>
+        <v>1241.2533</v>
       </c>
       <c r="C29" s="12" t="n">
-        <v>145.1572</v>
+        <v>150.7984</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>44.7884</v>
+        <v>50.8665</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>6615.916</v>
+        <v>6085.1083</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
@@ -1078,16 +1078,16 @@
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>587.5399</v>
+        <v>971.579</v>
       </c>
       <c r="C30" s="12" t="n">
-        <v>128.2897</v>
+        <v>204.5569</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>40.3893</v>
+        <v>51.6624</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>6102.0125</v>
+        <v>6142.5966</v>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
@@ -1097,16 +1097,16 @@
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>616.2147</v>
+        <v>923.9248</v>
       </c>
       <c r="C31" s="12" t="n">
-        <v>147.6737</v>
+        <v>151.3797</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>48.6105</v>
+        <v>51.5751</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>6647.4369</v>
+        <v>6019.6046</v>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
@@ -1116,16 +1116,16 @@
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>590.022</v>
+        <v>1543.0271</v>
       </c>
       <c r="C32" s="12" t="n">
-        <v>132.5524</v>
+        <v>200.0526</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>44.5325</v>
+        <v>57.1469</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>6050.4104</v>
+        <v>5337.442</v>
       </c>
     </row>
     <row r="33" ht="14" customHeight="1">
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>610.0405</v>
+        <v>1117.8486</v>
       </c>
       <c r="C33" s="12" t="n">
-        <v>1107.3776</v>
+        <v>150.1018</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>29.1002</v>
+        <v>54.6467</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>3837.774</v>
+        <v>5550.6905</v>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
@@ -1154,16 +1154,16 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>513.5242</v>
+        <v>804.6734</v>
       </c>
       <c r="C34" s="12" t="n">
-        <v>126.5667</v>
+        <v>199.158</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>39.3674</v>
+        <v>50.2456</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>5963.7138</v>
+        <v>6020.2563</v>
       </c>
     </row>
     <row r="35" ht="14" customHeight="1">
@@ -1173,16 +1173,16 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>547.4767000000001</v>
+        <v>793.8205</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>154.2922</v>
+        <v>178.0071</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>48.1367</v>
+        <v>49.8611</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>6456.8183</v>
+        <v>5667.9472</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
@@ -1192,16 +1192,16 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>641.2744</v>
+        <v>786.4318</v>
       </c>
       <c r="C36" s="12" t="n">
-        <v>147.6029</v>
+        <v>155.9928</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>48.95</v>
+        <v>46.3965</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>6446.3222</v>
+        <v>5643.6436</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
